--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -81,7 +81,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246402</t>
+          <t xml:space="preserve">10071260</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -90,7 +90,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>8883</v>
+        <v>1111</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10071260</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F3">
-        <v>1111</v>
+        <v>635</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">3231566</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F4">
-        <v>635</v>
+        <v>395</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,7 +231,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231566</t>
+          <t xml:space="preserve">3233530</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -240,7 +240,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233530</t>
+          <t xml:space="preserve">3235509</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>547</v>
+        <v>345</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>530</v>
+        <v>1504</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F8">
-        <v>285</v>
+        <v>660</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F9">
-        <v>334</v>
+        <v>583</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F10">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235509</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F11">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3245894</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>679</v>
+        <v>1251</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F13">
-        <v>1504</v>
+        <v>1022</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">3251702</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F14">
-        <v>660</v>
+        <v>307</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">3251934</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F15">
-        <v>583</v>
+        <v>1193</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>496</v>
+        <v>1453</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F17">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245894</t>
+          <t xml:space="preserve">3388073</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>1251</v>
+        <v>1786</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3388774</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F19">
-        <v>1022</v>
+        <v>371</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251702</t>
+          <t xml:space="preserve">389878</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>307</v>
+        <v>1788</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251934</t>
+          <t xml:space="preserve">389879</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>1193</v>
+        <v>562</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">389879</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22">
-        <v>289</v>
+        <v>952</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262653</t>
+          <t xml:space="preserve">389886, 389887, 389888</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>1113</v>
+        <v>2559</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>1453</v>
+        <v>374</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>420</v>
+        <v>4258</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388073</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26">
-        <v>1786</v>
+        <v>2413</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388774</t>
+          <t xml:space="preserve">389900, 389901</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>371</v>
+        <v>5756</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">389901</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F28">
-        <v>1616</v>
+        <v>294</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">409816, 409817</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>1554</v>
+        <v>2162</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F30">
-        <v>440</v>
+        <v>6215</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">389879</t>
+          <t xml:space="preserve">7239958</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>562</v>
+        <v>1555</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">389879</t>
+          <t xml:space="preserve">751619, 3221942</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F32">
-        <v>952</v>
+        <v>364</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">751671, 7473334</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>6215</v>
+        <v>1125</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7239958</t>
+          <t xml:space="preserve">751673, 3390783</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>1555</v>
+        <v>345</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">751619, 3221942</t>
+          <t xml:space="preserve">751676, 3391960</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">751671, 7473334</t>
+          <t xml:space="preserve">751677, 3388939</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F36">
-        <v>1125</v>
+        <v>2661</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">751673, 3390783</t>
+          <t xml:space="preserve">751679, 3391867</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F37">
-        <v>345</v>
+        <v>450</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">751676, 3391960</t>
+          <t xml:space="preserve">751681, 8826037</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>413</v>
+        <v>254</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">751677, 3388939</t>
+          <t xml:space="preserve">751686, 7922647</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>2661</v>
+        <v>261</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">751679, 3391867</t>
+          <t xml:space="preserve">8750185</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>450</v>
+        <v>731</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">751681, 8826037</t>
+          <t xml:space="preserve">9885411</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">751686, 7922647</t>
+          <t xml:space="preserve">751692, 7473334</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="F42">
-        <v>261</v>
+        <v>470</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010265</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-01-28</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2131,30 +2131,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">751687, 8124460</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43">
-        <v>2584</v>
+        <v>325</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014065</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-26</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">751692, 7473334</t>
+          <t xml:space="preserve">751687, 8124460</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="F44">
-        <v>470</v>
+        <v>2584</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016344</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>1054</v>
+        <v>4173</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022546</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,21 +2290,21 @@
         </is>
       </c>
       <c r="F46">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022546</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3251702</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>982</v>
+        <v>1582</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023228</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-02</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2386,25 +2386,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F48">
-        <v>1590</v>
+        <v>1054</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2431,30 +2431,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8750185</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F49">
-        <v>731</v>
+        <v>396</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2481,30 +2481,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134559</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F50">
-        <v>5565</v>
+        <v>982</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885411</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F51">
-        <v>269</v>
+        <v>1590</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">3242156</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>325</v>
+        <v>3862</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014065</t>
+          <t xml:space="preserve">200026043</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-26</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F53">
-        <v>643</v>
+        <v>530</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015937</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-25</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F54">
-        <v>4173</v>
+        <v>285</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022546</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-20</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F55">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022546</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-20</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251702</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F56">
-        <v>1582</v>
+        <v>473</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023228</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-02</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>1800</v>
+        <v>1424</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023940</t>
+          <t xml:space="preserve">200042900</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2020-12-14</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3258105</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>1220</v>
+        <v>2057</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023940</t>
+          <t xml:space="preserve">200044156</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3258247</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>4300</v>
+        <v>3505</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023940</t>
+          <t xml:space="preserve">200044154</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>2004</v>
+        <v>870</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023940</t>
+          <t xml:space="preserve">200044165</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242156</t>
+          <t xml:space="preserve">3391996</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>3862</v>
+        <v>1334</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026043</t>
+          <t xml:space="preserve">200045231</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">3391996</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F62">
-        <v>8065</v>
+        <v>3538</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042942</t>
+          <t xml:space="preserve">200045237</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-14</t>
+          <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">3257747</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>1424</v>
+        <v>2892</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042900</t>
+          <t xml:space="preserve">200045370</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-14</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232348</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="F64">
-        <v>3172</v>
+        <v>1013</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042902</t>
+          <t xml:space="preserve">200045365</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-14</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258105</t>
+          <t xml:space="preserve">3388939</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>2057</v>
+        <v>1989</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044156</t>
+          <t xml:space="preserve">200045366</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258247</t>
+          <t xml:space="preserve">3245971</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>3505</v>
+        <v>2037</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044154</t>
+          <t xml:space="preserve">200047894</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>870</v>
+        <v>5609</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044165</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391996</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F68">
-        <v>1334</v>
+        <v>1616</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045231</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-04</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391996</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F69">
-        <v>3538</v>
+        <v>643</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045237</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-04</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257747</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70">
-        <v>2892</v>
+        <v>1554</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045370</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F71">
-        <v>1013</v>
+        <v>440</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045365</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388939</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>1989</v>
+        <v>1800</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045366</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>5609</v>
+        <v>1220</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045631</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-15</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74">
-        <v>4258</v>
+        <v>679</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046144</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F75">
-        <v>2413</v>
+        <v>4300</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046145</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245971</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F76">
-        <v>2037</v>
+        <v>2004</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047894</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-11</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">389900, 389901</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F77">
-        <v>5756</v>
+        <v>449</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047945</t>
+          <t xml:space="preserve">311141837</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-12</t>
+          <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">3240143</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>449</v>
+        <v>772</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141837</t>
+          <t xml:space="preserve">311146695</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-26</t>
+          <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240143</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>772</v>
+        <v>283</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311146695</t>
+          <t xml:space="preserve">311147211</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-23</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3986,15 +3986,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>283</v>
+        <v>5012</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147211</t>
+          <t xml:space="preserve">311147212</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F81">
-        <v>5012</v>
+        <v>1840</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">3231646</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>1840</v>
+        <v>4245</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147212</t>
+          <t xml:space="preserve">311147235</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231646</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>4245</v>
+        <v>4595</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147235</t>
+          <t xml:space="preserve">311147290</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4186,11 +4186,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F84">
-        <v>4595</v>
+        <v>1014</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,20 +4231,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3233529</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>1014</v>
+        <v>3825</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147290</t>
+          <t xml:space="preserve">311147224</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233529</t>
+          <t xml:space="preserve">3239962</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>3825</v>
+        <v>2045</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147224</t>
+          <t xml:space="preserve">311147288</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239962</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="F87">
-        <v>2045</v>
+        <v>999</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147288</t>
+          <t xml:space="preserve">311147356</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4386,15 +4386,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F88">
-        <v>999</v>
+        <v>488</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147356</t>
+          <t xml:space="preserve">311147367</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4436,15 +4436,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F89">
-        <v>488</v>
+        <v>1405</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147367</t>
+          <t xml:space="preserve">311147369</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>1405</v>
+        <v>530</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147369</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">409816, 409817</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F91">
-        <v>2162</v>
+        <v>1424</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148091</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-01</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F92">
-        <v>530</v>
+        <v>995</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311161159</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">8369908</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>1424</v>
+        <v>383</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311163902</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">3262677</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>995</v>
+        <v>799</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311161159</t>
+          <t xml:space="preserve">311166177</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-26</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369908</t>
+          <t xml:space="preserve">3233518</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="F95">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163902</t>
+          <t xml:space="preserve">311168491</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-11</t>
+          <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262677</t>
+          <t xml:space="preserve">3239175</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>799</v>
+        <v>487</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166177</t>
+          <t xml:space="preserve">311169236</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233518</t>
+          <t xml:space="preserve">7752709</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="F97">
-        <v>434</v>
+        <v>912</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168491</t>
+          <t xml:space="preserve">311171770</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-05</t>
+          <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239175</t>
+          <t xml:space="preserve">9134559</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>487</v>
+        <v>5565</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169236</t>
+          <t xml:space="preserve">311172317</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752709</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>912</v>
+        <v>8065</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171770</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-20</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413132</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F100">
-        <v>1888</v>
+        <v>289</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179271</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5036,11 +5036,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F101">
-        <v>281</v>
+        <v>1888</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7584516</t>
+          <t xml:space="preserve">1413132</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F102">
-        <v>1115</v>
+        <v>281</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179947</t>
+          <t xml:space="preserve">311179271</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239487</t>
+          <t xml:space="preserve">7584516</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="F103">
-        <v>1164</v>
+        <v>1115</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181752</t>
+          <t xml:space="preserve">311179947</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-08</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3239487</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>428</v>
+        <v>1164</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190610</t>
+          <t xml:space="preserve">311181752</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-18</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,35 +5231,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242523</t>
+          <t xml:space="preserve">3262653</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>572</v>
+        <v>1113</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207345</t>
+          <t xml:space="preserve">311181777</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243120</t>
+          <t xml:space="preserve">7232348</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5290,26 +5290,26 @@
         </is>
       </c>
       <c r="F106">
-        <v>319</v>
+        <v>3172</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209474</t>
+          <t xml:space="preserve">311185935</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5331,35 +5331,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242161</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F107">
-        <v>840</v>
+        <v>428</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210030</t>
+          <t xml:space="preserve">311190610</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391896</t>
+          <t xml:space="preserve">3242523</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>635</v>
+        <v>572</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210142</t>
+          <t xml:space="preserve">311207345</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826071</t>
+          <t xml:space="preserve">3243120</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>575</v>
+        <v>319</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210311</t>
+          <t xml:space="preserve">311209474</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257468</t>
+          <t xml:space="preserve">3242161</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="F110">
-        <v>491</v>
+        <v>840</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210617</t>
+          <t xml:space="preserve">311210030</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258602</t>
+          <t xml:space="preserve">3391896</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>747</v>
+        <v>635</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212446</t>
+          <t xml:space="preserve">311210142</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258842</t>
+          <t xml:space="preserve">8826071</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212700</t>
+          <t xml:space="preserve">311210311</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">3257468</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>1422</v>
+        <v>491</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213714</t>
+          <t xml:space="preserve">311210617</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">3258602</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>557</v>
+        <v>747</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213892</t>
+          <t xml:space="preserve">311212446</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">3258842</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>3128</v>
+        <v>537</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214103</t>
+          <t xml:space="preserve">311212700</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F116">
-        <v>422</v>
+        <v>1422</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223668</t>
+          <t xml:space="preserve">311213714</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">389901</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>294</v>
+        <v>557</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225294</t>
+          <t xml:space="preserve">311213892</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235639</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>396</v>
+        <v>3128</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226663</t>
+          <t xml:space="preserve">311214103</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8275117</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F119">
-        <v>327</v>
+        <v>422</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226665</t>
+          <t xml:space="preserve">311223668</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7986826</t>
+          <t xml:space="preserve">3235639</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="F120">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229952</t>
+          <t xml:space="preserve">311226663</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7313030</t>
+          <t xml:space="preserve">8275117</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>944</v>
+        <v>327</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236277</t>
+          <t xml:space="preserve">311226665</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">7986826</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>3319</v>
+        <v>436</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287481</t>
+          <t xml:space="preserve">311229952</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">7313030</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F123">
-        <v>1558</v>
+        <v>944</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287487</t>
+          <t xml:space="preserve">311236277</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231805</t>
+          <t xml:space="preserve">100246402</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c r="F130">
-        <v>410</v>
+        <v>8883</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788173</t>
+          <t xml:space="preserve">311687096</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-29</t>
+          <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221313</t>
+          <t xml:space="preserve">3231805</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>1423</v>
+        <v>410</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853697</t>
+          <t xml:space="preserve">311788173</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-04</t>
+          <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8668873</t>
+          <t xml:space="preserve">3221313</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>254</v>
+        <v>1423</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873714</t>
+          <t xml:space="preserve">311853697</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">389886, 389887, 389888</t>
+          <t xml:space="preserve">8668873</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>2559</v>
+        <v>254</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888110</t>
+          <t xml:space="preserve">311873708</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F134">
-        <v>374</v>
+        <v>3319</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888109</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">389878</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F135">
-        <v>1788</v>
+        <v>1558</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901807</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-18</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">

--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:L136"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solkrogen 21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10071260</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1111</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rønnebærvej 14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">3221223</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>635</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sigsgaardsvej 18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231566</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>395</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbakvej 3A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233530</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>547</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammelgaardsvej 26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">3235509</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>345</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppelvej 1B</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243193</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1504</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppelvej 1A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243193</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>660</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppelvej 1C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243193</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>583</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">3244768</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>496</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">3244768</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>328</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terndrupvej 75</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">3245894</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1251</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 73</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">3249215</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1022</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uglevej 6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">3251702</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>307</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hammershøj 3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">3251934</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1193</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 24</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">3264061</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>1453</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">3264061</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>420</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Slettestrandvej 6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">3388073</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>1786</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klim Strandvej 5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">3388774</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>371</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">389878</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>1788</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Elmevej 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">389879</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>562</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mølleparken 1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">389879</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>952</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevej 8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">389886, 389887, 389888</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>2559</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>374</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aggersundvej 31</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">389895</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>4258</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aggersundvej 31</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">389895</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>2413</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aggersundvej 3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">389900, 389901</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>5756</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvænget 27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">389901</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>294</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammelgaardsvej 44</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">409816, 409817</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>2162</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 11</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">7232289</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>6215</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ilsigvej 21</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9492</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">7239958</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1555</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gjøl Havn 9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">751619, 3221942</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>364</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thorup Strandvej 329</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">751671, 7473334</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>1125</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aggersundvej 3B</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">751673, 3390783</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>345</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndumvej 25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">751676, 3391960</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>413</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thistedvej 320</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">751677, 3388939</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>2661</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Starkærvej 20</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">751679, 3391867</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>450</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Udklitvej 114</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">751681, 8826037</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>254</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thorup Strandvej 16B</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">751686, 7922647</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>261</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeslund Alle 4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">8750185</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>731</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torngårdsvej 16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">9885411</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>269</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thorup Strandvej 310</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">751692, 7473334</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>470</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">200010265</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-01-28</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 13</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">7232289</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>325</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">200014065</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-05-26</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 3B</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">751687, 8124460</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>2584</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">200016344</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 69</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">3249215</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>4173</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">200022546</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 69</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">3249215</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>253</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">200022546</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uglevej 6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">3251702</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1582</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">200023228</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-02</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>1054</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">200025972</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>396</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">200025972</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>982</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">200025972</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1590</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">200025972</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borgervænget 12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242156</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>3862</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">200026043</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanemosevej 45</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233735</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>530</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">200027513</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanemosevej 45</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233735</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>285</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">200027513</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanemosevej 45</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233735</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>334</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">200027513</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanemosevej 45</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233735</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>473</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">200027513</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 24</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">3264061</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>1424</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">200042900</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-12-14</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søparken 2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258105</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>2057</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">200044156</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftevej 43</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258247</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>3505</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">200044154</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 11</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">7232289</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>870</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">200044165</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danmarksgade 1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391996</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>1334</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">200045231</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danmarksgade 3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391996</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>3538</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">200045237</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Løthsvej 3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">3257747</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>2892</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">200045370</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjortdalvej 148</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">3387991</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1013</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">200045365</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klim Strandvej 11</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">3388939</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1989</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">200045366</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">3245971</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>2037</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">200047894</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borups Alle 8</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391975</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>5609</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">200047992</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borups Alle 8</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391975</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>1616</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">200047992</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnevej 10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391975</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>643</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">200047992</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borups Alle 8</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391975</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>1554</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">200047992</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Borups Alle 8</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391975</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>440</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">200047992</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242263</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1800</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311139958</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242263</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1220</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311139958</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242263</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>679</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311139958</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242263</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>4300</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311139958</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242263</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>2004</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311139958</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 6</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231236</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>449</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311141837</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assenbækvej 2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9700</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">3240143</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>772</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311146695</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231236</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>283</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311147211</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231236</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>5012</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311147212</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231236</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>1840</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311147212</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredgade 101</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231646</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>4245</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311147235</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blokhusvej 41</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">3232158</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>4595</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311147290</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blokhusvej 43</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">3232158</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>1014</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311147290</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbakvej 5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233529</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>3825</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311147224</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gerdsvej 1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9700</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">3239962</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>2045</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311147288</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>999</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311147356</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>488</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311147367</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nolsvej 1A</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">7898532</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>1405</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311147369</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 3</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">3244768</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>530</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311149340</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">3244768</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>1424</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311149340</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstegaardsvej 26A</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">3227505</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>995</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311161159</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thomasmindeparken 1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">8369908</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>383</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311163902</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sundbyvej 30</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">3262677</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>799</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311166177</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbakvej 1D</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">3233518</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>434</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311168491</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjorthsvej 7</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">3239175</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>487</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311169236</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Løthsvej 10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">7752709</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>912</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311171770</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">9134559</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>5565</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311172317</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kattedamsvej 26</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258634</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>8065</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311178208</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kattedamsvej 34</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258634</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>289</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311178208</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">1413132</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>1888</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311179271</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">1413132</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>281</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311179271</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkevangen 4</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">7584516</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>1115</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311179947</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl. Landevej 62C</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">3239487</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>1164</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311181752</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 15A</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">3262653</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>1113</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311181777</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl. Landevej 70</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">7232348</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>3172</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311185935</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Blokhusvej 47A</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">3232158</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>428</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311190610</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Elmevej 6</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242523</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>572</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311207345</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnevænget 1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243120</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>319</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311209474</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rotfelds Vej 11</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242161</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>840</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311210030</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vester Fælledvej 17</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">3391896</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>635</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311210142</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svinkløvvej 1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">8826071</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>575</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311210311</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Viaduktvej 28A</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">3257468</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>491</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311210617</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skipper Clements Vej 25</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258602</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>747</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311212446</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Anlægsvej 1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258842</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>537</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311212700</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rønnebærvej 8</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">3221223</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>1422</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311213714</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ørebrovej 128</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">9009874</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>557</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311213892</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ørebrovej 128</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">9009874</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>3128</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311214103</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørtorupvej 2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9690</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">3387991</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>422</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311223668</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kordalsvej 13</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9493</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">3235639</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>396</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311226663</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøge Bakker 7</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">8275117</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>327</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311226665</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6081,33 +7291,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Niels Juels Vej 1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">7986826</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>436</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311229952</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6131,33 +7351,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østmarken 2</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9430</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t xml:space="preserve">7313030</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="H123">
         <v>944</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">311236277</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6181,33 +7411,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstegaardsvej 34</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t xml:space="preserve">3227457</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="H124">
         <v>519</v>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">311430955</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6231,33 +7471,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstegaardsvej 26C</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t xml:space="preserve">3227505</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>296</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">311430960</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6281,33 +7531,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stationsvej 20</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t xml:space="preserve">3242155</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>2615</v>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">311502859</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-12</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,33 +7591,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258795</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>7053</v>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t xml:space="preserve">311680518</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6381,33 +7651,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258795</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>1233</v>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t xml:space="preserve">311680518</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="K128" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6431,33 +7711,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258795</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>413</v>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">311680518</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6481,33 +7771,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t xml:space="preserve">100246402</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="H130">
         <v>8883</v>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t xml:space="preserve">311687096</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6531,33 +7831,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Possementmagervej 1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9490</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t xml:space="preserve">3231805</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="H131">
         <v>410</v>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t xml:space="preserve">311788173</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6581,33 +7891,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rønnebærvej 12A</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t xml:space="preserve">3221313</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="H132">
         <v>1423</v>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">311853697</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6631,33 +7951,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 143A</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t xml:space="preserve">8668873</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="H133">
         <v>254</v>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311873708</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311873714</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6681,33 +8011,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sygehusvej 14</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243191</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="H134">
         <v>3319</v>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">311898289</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="K134" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6731,33 +8071,43 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sygehusvej 6</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9460</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t xml:space="preserve">3243191</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F135">
+      <c r="H135">
         <v>1558</v>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t xml:space="preserve">311898289</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6781,39 +8131,49 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kattedamsvej 32B</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9440</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t xml:space="preserve">3258634</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F136">
+      <c r="H136">
         <v>1552</v>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t xml:space="preserve">311902872</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="K136" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J136"/>
+  <autoFilter ref="A1:L136"/>
 </worksheet>
 </file>
--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solkrogen 21</t>
+          <t xml:space="preserve">Aggersundvej 3B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,7 +101,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10071260</t>
+          <t xml:space="preserve">751673, 3390783</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>1111</v>
+        <v>345</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 14</t>
+          <t xml:space="preserve">Brøndumvej 25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">751676, 3391960</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>635</v>
+        <v>413</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigsgaardsvej 18</t>
+          <t xml:space="preserve">Bygaden 24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231566</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>395</v>
+        <v>1453</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 3A</t>
+          <t xml:space="preserve">Bygaden 24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233530</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>547</v>
+        <v>420</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgaardsvej 26</t>
+          <t xml:space="preserve">Elmevej 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235509</t>
+          <t xml:space="preserve">389879</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>345</v>
+        <v>562</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,17 +391,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 1B</t>
+          <t xml:space="preserve">Gammelgaardsvej 26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">3235509</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c r="H7">
-        <v>1504</v>
+        <v>345</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 1A</t>
+          <t xml:space="preserve">Gjøl Havn 9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">751619, 3221942</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H8">
-        <v>660</v>
+        <v>364</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 1C</t>
+          <t xml:space="preserve">Hammershøj 3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243193</t>
+          <t xml:space="preserve">3251934</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H9">
-        <v>583</v>
+        <v>1193</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Hovedgaden 73</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H10">
-        <v>496</v>
+        <v>1022</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H11">
-        <v>328</v>
+        <v>6215</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terndrupvej 75</t>
+          <t xml:space="preserve">Ilsigvej 21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9492</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245894</t>
+          <t xml:space="preserve">7239958</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="H12">
-        <v>1251</v>
+        <v>1555</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 73</t>
+          <t xml:space="preserve">Klim Strandvej 5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3388774</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H13">
-        <v>1022</v>
+        <v>371</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uglevej 6</t>
+          <t xml:space="preserve">Langeslund Alle 4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251702</t>
+          <t xml:space="preserve">8750185</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>307</v>
+        <v>731</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershøj 3</t>
+          <t xml:space="preserve">Lundbakvej 3A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251934</t>
+          <t xml:space="preserve">3233530</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H15">
-        <v>1193</v>
+        <v>547</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 24</t>
+          <t xml:space="preserve">Mølleparken 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">389879</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>1453</v>
+        <v>952</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 24</t>
+          <t xml:space="preserve">Poppelvej 1A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettestrandvej 6</t>
+          <t xml:space="preserve">Poppelvej 1B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388073</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>1786</v>
+        <v>1504</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klim Strandvej 5</t>
+          <t xml:space="preserve">Poppelvej 1C</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388774</t>
+          <t xml:space="preserve">3243193</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H19">
-        <v>371</v>
+        <v>583</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 9</t>
+          <t xml:space="preserve">Rønnebærvej 14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">389878</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H20">
-        <v>1788</v>
+        <v>635</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmevej 1</t>
+          <t xml:space="preserve">Sigsgaardsvej 18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">389879</t>
+          <t xml:space="preserve">3231566</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H21">
-        <v>562</v>
+        <v>395</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mølleparken 1</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">389879</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H22">
-        <v>952</v>
+        <v>496</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 8</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">389886, 389887, 389888</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H23">
-        <v>2559</v>
+        <v>328</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 28</t>
+          <t xml:space="preserve">Slettestrandvej 6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
+          <t xml:space="preserve">3388073</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>374</v>
+        <v>1786</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 31</t>
+          <t xml:space="preserve">Solkrogen 21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">10071260</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>4258</v>
+        <v>1111</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 31</t>
+          <t xml:space="preserve">Starkærvej 20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">389895</t>
+          <t xml:space="preserve">751679, 3391867</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H26">
-        <v>2413</v>
+        <v>450</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 3</t>
+          <t xml:space="preserve">Terndrupvej 75</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">389900, 389901</t>
+          <t xml:space="preserve">3245894</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>5756</v>
+        <v>1251</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvænget 27</t>
+          <t xml:space="preserve">Thistedvej 320</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">389901</t>
+          <t xml:space="preserve">751677, 3388939</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H28">
-        <v>294</v>
+        <v>2661</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgaardsvej 44</t>
+          <t xml:space="preserve">Thorup Strandvej 16B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">409816, 409817</t>
+          <t xml:space="preserve">751686, 7922647</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H29">
-        <v>2162</v>
+        <v>261</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Thorup Strandvej 329</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">751671, 7473334</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>6215</v>
+        <v>1125</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilsigvej 21</t>
+          <t xml:space="preserve">Torngårdsvej 16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7239958</t>
+          <t xml:space="preserve">9885411</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="H31">
-        <v>1555</v>
+        <v>269</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gjøl Havn 9</t>
+          <t xml:space="preserve">Udklitvej 114</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">751619, 3221942</t>
+          <t xml:space="preserve">751681, 8826037</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>364</v>
+        <v>254</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorup Strandvej 329</t>
+          <t xml:space="preserve">Uglevej 6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">751671, 7473334</t>
+          <t xml:space="preserve">3251702</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="H33">
-        <v>1125</v>
+        <v>307</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggersundvej 3B</t>
+          <t xml:space="preserve">Thorup Strandvej 310</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">751673, 3390783</t>
+          <t xml:space="preserve">751692, 7473334</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="H34">
-        <v>345</v>
+        <v>470</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010265</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-01-28</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2071,40 +2071,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndumvej 25</t>
+          <t xml:space="preserve">Idrætsvej 13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">751676, 3391960</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H35">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014065</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-26</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thistedvej 320</t>
+          <t xml:space="preserve">Skolevænget 3B</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,30 +2141,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">751677, 3388939</t>
+          <t xml:space="preserve">751687, 8124460</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>2661</v>
+        <v>2584</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016344</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2191,40 +2191,40 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starkærvej 20</t>
+          <t xml:space="preserve">Hovedgaden 69</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">751679, 3391867</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>450</v>
+        <v>4173</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022546</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2251,40 +2251,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udklitvej 114</t>
+          <t xml:space="preserve">Hovedgaden 69</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">751681, 8826037</t>
+          <t xml:space="preserve">3249215</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022546</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorup Strandvej 16B</t>
+          <t xml:space="preserve">Uglevej 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">751686, 7922647</t>
+          <t xml:space="preserve">3251702</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="H39">
-        <v>261</v>
+        <v>1582</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023228</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-02</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2371,40 +2371,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langeslund Alle 4</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8750185</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H40">
-        <v>731</v>
+        <v>1054</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2431,40 +2431,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torngårdsvej 16</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885411</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H41">
-        <v>269</v>
+        <v>396</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorup Strandvej 310</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">751692, 7473334</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H42">
-        <v>470</v>
+        <v>982</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010265</t>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-01-28</t>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 13</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H43">
-        <v>325</v>
+        <v>1590</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014065</t>
+          <t xml:space="preserve">200025972</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-26</t>
+          <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3B</t>
+          <t xml:space="preserve">Borgervænget 12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">751687, 8124460</t>
+          <t xml:space="preserve">3242156</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="H44">
-        <v>2584</v>
+        <v>3862</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016344</t>
+          <t xml:space="preserve">200026043</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69</t>
+          <t xml:space="preserve">Svanemosevej 45</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H45">
-        <v>4173</v>
+        <v>530</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022546</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-20</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69</t>
+          <t xml:space="preserve">Svanemosevej 45</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249215</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H46">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022546</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-20</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,35 +2791,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uglevej 6</t>
+          <t xml:space="preserve">Svanemosevej 45</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251702</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H47">
-        <v>1582</v>
+        <v>334</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023228</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-02</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Svanemosevej 45</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3233735</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H48">
-        <v>1054</v>
+        <v>473</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025972</t>
+          <t xml:space="preserve">200027513</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-21</t>
+          <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Bygaden 24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3264061</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>396</v>
+        <v>1424</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025972</t>
+          <t xml:space="preserve">200042900</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-21</t>
+          <t xml:space="preserve">2020-12-14</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">7232289</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>982</v>
+        <v>870</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025972</t>
+          <t xml:space="preserve">200044165</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-21</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Søparken 2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3258105</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>1590</v>
+        <v>2057</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025972</t>
+          <t xml:space="preserve">200044156</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-21</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgervænget 12</t>
+          <t xml:space="preserve">Toftevej 43</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242156</t>
+          <t xml:space="preserve">3258247</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>3862</v>
+        <v>3505</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026043</t>
+          <t xml:space="preserve">200044154</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-22</t>
+          <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,35 +3151,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosevej 45</t>
+          <t xml:space="preserve">Danmarksgade 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3391996</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>530</v>
+        <v>1334</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027513</t>
+          <t xml:space="preserve">200045231</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosevej 45</t>
+          <t xml:space="preserve">Danmarksgade 3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3391996</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H54">
-        <v>285</v>
+        <v>3538</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027513</t>
+          <t xml:space="preserve">200045237</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosevej 45</t>
+          <t xml:space="preserve">Hjortdalvej 148</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>334</v>
+        <v>1013</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027513</t>
+          <t xml:space="preserve">200045365</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosevej 45</t>
+          <t xml:space="preserve">Klim Strandvej 11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233735</t>
+          <t xml:space="preserve">3388939</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>473</v>
+        <v>1989</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027513</t>
+          <t xml:space="preserve">200045366</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-01</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 24</t>
+          <t xml:space="preserve">Peter Løthsvej 3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264061</t>
+          <t xml:space="preserve">3257747</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>1424</v>
+        <v>2892</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042900</t>
+          <t xml:space="preserve">200045370</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-14</t>
+          <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 2</t>
+          <t xml:space="preserve">Aggersundvej 31</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258105</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>2057</v>
+        <v>4258</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044156</t>
+          <t xml:space="preserve">200046144</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 43</t>
+          <t xml:space="preserve">Aggersundvej 31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258247</t>
+          <t xml:space="preserve">389895</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>3505</v>
+        <v>2413</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044154</t>
+          <t xml:space="preserve">200046145</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232289</t>
+          <t xml:space="preserve">3245971</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>870</v>
+        <v>2037</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044165</t>
+          <t xml:space="preserve">200047894</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-11</t>
+          <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 1</t>
+          <t xml:space="preserve">Aggersundvej 3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391996</t>
+          <t xml:space="preserve">389900, 389901</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,16 +3650,16 @@
         </is>
       </c>
       <c r="H61">
-        <v>1334</v>
+        <v>5756</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045231</t>
+          <t xml:space="preserve">200047945</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-04</t>
+          <t xml:space="preserve">2021-04-12</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 3</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391996</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>3538</v>
+        <v>5609</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045237</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-04</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 3</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257747</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H63">
-        <v>2892</v>
+        <v>1616</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045370</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortdalvej 148</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1013</v>
+        <v>1554</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045365</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klim Strandvej 11</t>
+          <t xml:space="preserve">Borups Alle 8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3388939</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H65">
-        <v>1989</v>
+        <v>440</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045366</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-08</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Tjørnevej 10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3245971</t>
+          <t xml:space="preserve">3391975</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H66">
-        <v>2037</v>
+        <v>643</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047894</t>
+          <t xml:space="preserve">200047992</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-11</t>
+          <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>5609</v>
+        <v>1800</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>1616</v>
+        <v>1220</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 10</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H69">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H70">
-        <v>1554</v>
+        <v>4300</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borups Alle 8</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391975</t>
+          <t xml:space="preserve">3242263</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H71">
-        <v>440</v>
+        <v>2004</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047992</t>
+          <t xml:space="preserve">311139958</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-13</t>
+          <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H72">
-        <v>1800</v>
+        <v>449</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311141837</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Assenbækvej 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3240143</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>1220</v>
+        <v>772</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311146695</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Blokhusvej 41</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>679</v>
+        <v>4595</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311147290</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Blokhusvej 43</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H75">
-        <v>4300</v>
+        <v>1014</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311147290</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Bredgade 101</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242263</t>
+          <t xml:space="preserve">3231646</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>2004</v>
+        <v>4245</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139958</t>
+          <t xml:space="preserve">311147235</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-13</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Gerdsvej 1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9700</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">3239962</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>449</v>
+        <v>2045</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141837</t>
+          <t xml:space="preserve">311147288</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-26</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assenbækvej 2</t>
+          <t xml:space="preserve">Lundbakvej 5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240143</t>
+          <t xml:space="preserve">3233529</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>772</v>
+        <v>3825</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311146695</t>
+          <t xml:space="preserve">311147224</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-23</t>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Nolsvej 1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,11 +4730,11 @@
         </is>
       </c>
       <c r="H79">
-        <v>283</v>
+        <v>999</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147211</t>
+          <t xml:space="preserve">311147356</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,30 +4771,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4</t>
+          <t xml:space="preserve">Nolsvej 1A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H80">
-        <v>5012</v>
+        <v>1405</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147212</t>
+          <t xml:space="preserve">311147369</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,30 +4831,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4</t>
+          <t xml:space="preserve">Nolsvej 3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231236</t>
+          <t xml:space="preserve">7898532</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H81">
-        <v>1840</v>
+        <v>488</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147212</t>
+          <t xml:space="preserve">311147367</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 101</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231646</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,11 +4910,11 @@
         </is>
       </c>
       <c r="H82">
-        <v>4245</v>
+        <v>283</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147235</t>
+          <t xml:space="preserve">311147211</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 41</t>
+          <t xml:space="preserve">Skolegade 4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,20 +4961,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>4595</v>
+        <v>5012</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147290</t>
+          <t xml:space="preserve">311147212</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 43</t>
+          <t xml:space="preserve">Skolegade 4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,20 +5021,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3231236</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H84">
-        <v>1014</v>
+        <v>1840</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147290</t>
+          <t xml:space="preserve">311147212</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 5</t>
+          <t xml:space="preserve">Gammelgaardsvej 44</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233529</t>
+          <t xml:space="preserve">409816, 409817</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>3825</v>
+        <v>2162</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147224</t>
+          <t xml:space="preserve">311148091</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-01</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerdsvej 1</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239962</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>2045</v>
+        <v>530</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147288</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3244768</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H87">
-        <v>999</v>
+        <v>1424</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147356</t>
+          <t xml:space="preserve">311149340</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 3</t>
+          <t xml:space="preserve">Præstegaardsvej 26A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H88">
-        <v>488</v>
+        <v>995</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147367</t>
+          <t xml:space="preserve">311161159</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nolsvej 1A</t>
+          <t xml:space="preserve">Thomasmindeparken 1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898532</t>
+          <t xml:space="preserve">8369908</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>1405</v>
+        <v>383</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311147369</t>
+          <t xml:space="preserve">311163902</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-25</t>
+          <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Sundbyvej 30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3262677</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>530</v>
+        <v>799</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311166177</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Lundbakvej 1D</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3244768</t>
+          <t xml:space="preserve">3233518</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>1424</v>
+        <v>434</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311149340</t>
+          <t xml:space="preserve">311168491</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-08</t>
+          <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26A</t>
+          <t xml:space="preserve">Hjorthsvej 7</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">3239175</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>995</v>
+        <v>487</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311161159</t>
+          <t xml:space="preserve">311169236</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-26</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomasmindeparken 1</t>
+          <t xml:space="preserve">Peter Løthsvej 10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369908</t>
+          <t xml:space="preserve">7752709</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,16 +5570,16 @@
         </is>
       </c>
       <c r="H93">
-        <v>383</v>
+        <v>912</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311163902</t>
+          <t xml:space="preserve">311171770</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-11</t>
+          <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundbyvej 30</t>
+          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262677</t>
+          <t xml:space="preserve">9134559</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>799</v>
+        <v>5565</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311166177</t>
+          <t xml:space="preserve">311172317</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-21</t>
+          <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbakvej 1D</t>
+          <t xml:space="preserve">Kattedamsvej 26</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233518</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>434</v>
+        <v>8065</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168491</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-05</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjorthsvej 7</t>
+          <t xml:space="preserve">Kattedamsvej 34</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239175</t>
+          <t xml:space="preserve">3258634</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H96">
-        <v>487</v>
+        <v>289</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169236</t>
+          <t xml:space="preserve">311178208</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Løthsvej 10</t>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752709</t>
+          <t xml:space="preserve">1413132</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>912</v>
+        <v>1888</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311171770</t>
+          <t xml:space="preserve">311179271</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-20</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaby Sdr. Gade 35</t>
+          <t xml:space="preserve">Gustav Zimmersvej 29</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134559</t>
+          <t xml:space="preserve">1413132</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>5565</v>
+        <v>281</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311172317</t>
+          <t xml:space="preserve">311179271</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 26</t>
+          <t xml:space="preserve">Birkevangen 4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">7584516</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>8065</v>
+        <v>1115</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178208</t>
+          <t xml:space="preserve">311179947</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-23</t>
+          <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattedamsvej 34</t>
+          <t xml:space="preserve">Gl. Landevej 62C</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258634</t>
+          <t xml:space="preserve">3239487</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>289</v>
+        <v>1164</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178208</t>
+          <t xml:space="preserve">311181752</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-23</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+          <t xml:space="preserve">Idrætsvej 15A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413132</t>
+          <t xml:space="preserve">3262653</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>1888</v>
+        <v>1113</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179271</t>
+          <t xml:space="preserve">311181777</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Zimmersvej 29</t>
+          <t xml:space="preserve">Gl. Landevej 70</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413132</t>
+          <t xml:space="preserve">7232348</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>281</v>
+        <v>3172</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179271</t>
+          <t xml:space="preserve">311185935</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevangen 4</t>
+          <t xml:space="preserve">Blokhusvej 47A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7584516</t>
+          <t xml:space="preserve">3232158</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H103">
-        <v>1115</v>
+        <v>428</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179947</t>
+          <t xml:space="preserve">311190610</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-31</t>
+          <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 62C</t>
+          <t xml:space="preserve">Elmevej 6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3239487</t>
+          <t xml:space="preserve">3242523</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,26 +6230,26 @@
         </is>
       </c>
       <c r="H104">
-        <v>1164</v>
+        <v>572</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181752</t>
+          <t xml:space="preserve">311207345</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-08</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6271,45 +6271,45 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 15A</t>
+          <t xml:space="preserve">Tjørnevænget 1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262653</t>
+          <t xml:space="preserve">3243120</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>1113</v>
+        <v>319</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181777</t>
+          <t xml:space="preserve">311209474</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-08</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6331,17 +6331,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 70</t>
+          <t xml:space="preserve">Rotfelds Vej 11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232348</t>
+          <t xml:space="preserve">3242161</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6350,26 +6350,26 @@
         </is>
       </c>
       <c r="H106">
-        <v>3172</v>
+        <v>840</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185935</t>
+          <t xml:space="preserve">311210030</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-27</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6391,45 +6391,45 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blokhusvej 47A</t>
+          <t xml:space="preserve">Vester Fælledvej 17</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3232158</t>
+          <t xml:space="preserve">3391896</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>428</v>
+        <v>635</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190610</t>
+          <t xml:space="preserve">311210142</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-18</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6451,17 +6451,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmevej 6</t>
+          <t xml:space="preserve">Svinkløvvej 1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242523</t>
+          <t xml:space="preserve">8826071</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207345</t>
+          <t xml:space="preserve">311210311</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevænget 1</t>
+          <t xml:space="preserve">Viaduktvej 28A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243120</t>
+          <t xml:space="preserve">3257468</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>319</v>
+        <v>491</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209474</t>
+          <t xml:space="preserve">311210617</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotfelds Vej 11</t>
+          <t xml:space="preserve">Skipper Clements Vej 25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242161</t>
+          <t xml:space="preserve">3258602</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="H110">
-        <v>840</v>
+        <v>747</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210030</t>
+          <t xml:space="preserve">311212446</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Fælledvej 17</t>
+          <t xml:space="preserve">Anlægsvej 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3391896</t>
+          <t xml:space="preserve">3258842</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>635</v>
+        <v>537</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210142</t>
+          <t xml:space="preserve">311212700</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinkløvvej 1</t>
+          <t xml:space="preserve">Rønnebærvej 8</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826071</t>
+          <t xml:space="preserve">3221223</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>575</v>
+        <v>1422</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210311</t>
+          <t xml:space="preserve">311213714</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 28A</t>
+          <t xml:space="preserve">Ørebrovej 128</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257468</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H113">
-        <v>491</v>
+        <v>557</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210617</t>
+          <t xml:space="preserve">311213892</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skipper Clements Vej 25</t>
+          <t xml:space="preserve">Ørebrovej 128</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258602</t>
+          <t xml:space="preserve">9009874</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>747</v>
+        <v>3128</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212446</t>
+          <t xml:space="preserve">311214103</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsvej 1</t>
+          <t xml:space="preserve">Nørtorupvej 2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258842</t>
+          <t xml:space="preserve">3387991</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H115">
-        <v>537</v>
+        <v>422</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212700</t>
+          <t xml:space="preserve">311223668</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 8</t>
+          <t xml:space="preserve">Parkvænget 27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9690</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221223</t>
+          <t xml:space="preserve">389901</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>1422</v>
+        <v>294</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213714</t>
+          <t xml:space="preserve">311225294</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørebrovej 128</t>
+          <t xml:space="preserve">Bøge Bakker 7</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">8275117</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>557</v>
+        <v>327</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213892</t>
+          <t xml:space="preserve">311226665</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørebrovej 128</t>
+          <t xml:space="preserve">Kordalsvej 13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9493</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9009874</t>
+          <t xml:space="preserve">3235639</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>3128</v>
+        <v>396</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214103</t>
+          <t xml:space="preserve">311226663</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,35 +7111,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørtorupvej 2</t>
+          <t xml:space="preserve">Niels Juels Vej 1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387991</t>
+          <t xml:space="preserve">7986826</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H119">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223668</t>
+          <t xml:space="preserve">311229952</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kordalsvej 13</t>
+          <t xml:space="preserve">Østmarken 2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9493</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3235639</t>
+          <t xml:space="preserve">7313030</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H120">
-        <v>396</v>
+        <v>944</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226663</t>
+          <t xml:space="preserve">311236277</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøge Bakker 7</t>
+          <t xml:space="preserve">Præstegaardsvej 26C</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8275117</t>
+          <t xml:space="preserve">3227505</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H121">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226665</t>
+          <t xml:space="preserve">311430960</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Juels Vej 1</t>
+          <t xml:space="preserve">Præstegaardsvej 34</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7986826</t>
+          <t xml:space="preserve">3227457</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7310,16 +7310,16 @@
         </is>
       </c>
       <c r="H122">
-        <v>436</v>
+        <v>519</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229952</t>
+          <t xml:space="preserve">311430955</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,35 +7351,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østmarken 2</t>
+          <t xml:space="preserve">Stationsvej 20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7313030</t>
+          <t xml:space="preserve">3242155</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>944</v>
+        <v>2615</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236277</t>
+          <t xml:space="preserve">311502859</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2031-03-12</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 34</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227457</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>519</v>
+        <v>7053</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430955</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 26C</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3227505</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H125">
-        <v>296</v>
+        <v>1233</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430960</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-31</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,35 +7531,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 20</t>
+          <t xml:space="preserve">Jens Møllersvej 3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9460</t>
+          <t xml:space="preserve">9440</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3242155</t>
+          <t xml:space="preserve">3258795</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H126">
-        <v>2615</v>
+        <v>413</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502859</t>
+          <t xml:space="preserve">311680518</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-12</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">100246402</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>7053</v>
+        <v>8883</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311687096</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Possementmagervej 1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9490</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">3231805</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>1233</v>
+        <v>410</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311788173</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Møllersvej 3</t>
+          <t xml:space="preserve">Rønnebærvej 12A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,25 +7721,25 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3258795</t>
+          <t xml:space="preserve">3221313</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H129">
-        <v>413</v>
+        <v>1423</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680518</t>
+          <t xml:space="preserve">311853697</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jetsmark Kirkevej 5</t>
+          <t xml:space="preserve">Strandvejen 143A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100246402</t>
+          <t xml:space="preserve">8668873</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>8883</v>
+        <v>254</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311687096</t>
+          <t xml:space="preserve">311873714</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-12</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Possementmagervej 1</t>
+          <t xml:space="preserve">Egevej 8</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231805</t>
+          <t xml:space="preserve">389886, 389887, 389888</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>410</v>
+        <v>2559</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788173</t>
+          <t xml:space="preserve">311888110</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-29</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnebærvej 12A</t>
+          <t xml:space="preserve">Parkvej 28</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9440</t>
+          <t xml:space="preserve">9460</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3221313</t>
+          <t xml:space="preserve">389889, 389890, 389891, 389892, 389893, 389894</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H132">
-        <v>1423</v>
+        <v>374</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853697</t>
+          <t xml:space="preserve">311888109</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-04</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 143A</t>
+          <t xml:space="preserve">Sygehusvej 14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8668873</t>
+          <t xml:space="preserve">3243191</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="H133">
-        <v>254</v>
+        <v>3319</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873714</t>
+          <t xml:space="preserve">311898289</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 14</t>
+          <t xml:space="preserve">Sygehusvej 6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8026,11 +8026,11 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H134">
-        <v>3319</v>
+        <v>1558</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sygehusvej 6</t>
+          <t xml:space="preserve">Vestergade 9</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3243191</t>
+          <t xml:space="preserve">389878</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>1558</v>
+        <v>1788</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898289</t>
+          <t xml:space="preserve">311901807</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-01</t>
+          <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">

--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:M136"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOLIUS Boligejernes Videncenter A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-01-28</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-26</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-20</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-02</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-21</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-22</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-01</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-14</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-11</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-04</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-08</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-11</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-12</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-13</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-13</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-26</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-23</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-01</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-08</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-26</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-11</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-21</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-05</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-20</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Infrarød Inspektion A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-23</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-05-31</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-18</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">JPH Energi A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-31</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-12</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Preben Dam ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Preben Dam ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Preben Dam ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-12</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-29</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-04</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Preben Dam ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Komplet Rådgivning IVS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-18</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,21 +8834,26 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L136"/>
+  <autoFilter ref="A1:M136"/>
 </worksheet>
 </file>
--- a/public/exports/29189439.xlsx
+++ b/public/exports/29189439.xlsx
@@ -8439,12 +8439,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873714</t>
+          <t xml:space="preserve">311873708</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preben Dam ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K130" t="inlineStr">
